--- a/проект/INTERNATIONAL_PRACTICES.xlsx
+++ b/проект/INTERNATIONAL_PRACTICES.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2088,6 +2088,43 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>I-easyread</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Великобритания: Accessible Information Standard — информация для пациентов с нарушениями предоставляется в доступных форматах (включая easy read: короткие фразы + изображения); Mencap — методические материалы</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NHS England / Mencap, Великобритания</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.mencap.org.uk/help-and-advice/health/accessible-information-standard</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>проверено 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>глава 15, приложение 38 (памятка easy read)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/проект/INTERNATIONAL_PRACTICES.xlsx
+++ b/проект/INTERNATIONAL_PRACTICES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Международные практики" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Международные практики" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Международные практики'!$A$1:$G$44</definedName>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>верифицировано 21–23.07.2026; перенесено 23.07.2026; редакции 2025–2026 перепроверены точечно (Standard 6 вступил 01.11.2025)</t>
+          <t>вторичный коммерческий обзор (comimi.jp); первоисточник — материалы MHLW, построчно не сверен; число 87–94% используется как порядок охвата, не как первичные данные. верифицировано 21–23.07.2026; перенесено 23.07.2026; редакции 2025–2026 перепроверены точечно (Standard 6 вступил 01.11.2025)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1911,27 +1911,27 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Число диетологов и госпитализации: 2 vs 1 — 20,3% vs 30,6%</t>
+          <t>Больше диетологов в штате дома → ниже риск потенциально предотвратимых госпитализаций: скоррект. HR 0,72 (95% ДИ 0,54–0,97); ретроспективная когорта 2909 жителей 235 домов</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Япония</t>
+          <t>BMC Geriatrics (Ибараки, Япония), 2023; ст. 566; DOI 10.1186/s12877-023-04278-2</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://rehab.cloud/mag/2862/</t>
+          <t>https://doi.org/10.1186/s12877-023-04278-2</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>верифицировано 21–23.07.2026; перенесено 23.07.2026; редакции 2025–2026 перепроверены точечно (Standard 6 вступил 01.11.2025)</t>
+          <t>первоисточник сверен по BMC Geriatrics 2023 (доступ 23.08.2026); прежняя ссылка rehab.cloud (вторичный блог) и число «20,3% vs 30,6%» ошибочны — 20,3% в одном обзоре был response rate, не госпитализацией; заменено на HR 0,72</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
